--- a/public/baocao1.xlsx
+++ b/public/baocao1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="459">
   <si>
     <t>STT</t>
   </si>
@@ -45,6 +45,1353 @@
   </si>
   <si>
     <t>Tình trạng sản phẩm</t>
+  </si>
+  <si>
+    <t>Cửa Hàng Hồng Phát</t>
+  </si>
+  <si>
+    <t>28 Ngô Quyền, Tân An</t>
+  </si>
+  <si>
+    <t>0292.3822.967</t>
+  </si>
+  <si>
+    <t>Bếp điện 1 từ 1 hồng ngoại EI-6226</t>
+  </si>
+  <si>
+    <t>BĐTHNEI-6226</t>
+  </si>
+  <si>
+    <t>210408b7231bc71a</t>
+  </si>
+  <si>
+    <t>02-07-2024</t>
+  </si>
+  <si>
+    <t>Chưa cấu hình</t>
+  </si>
+  <si>
+    <t>Chưa Kích Hoạt</t>
+  </si>
+  <si>
+    <t>NPP Vạn Hạnh LĐ</t>
+  </si>
+  <si>
+    <t>Khu Bạch Đằng, Nam Ban</t>
+  </si>
+  <si>
+    <t>0961.942.389</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ CA-9979</t>
+  </si>
+  <si>
+    <t>BĐTCA-9979</t>
+  </si>
+  <si>
+    <t>210408f3a625468a</t>
+  </si>
+  <si>
+    <t>Nam Phú  Nhà Bè</t>
+  </si>
+  <si>
+    <t>0917201207</t>
+  </si>
+  <si>
+    <t>Hút khói Civina CV-700T</t>
+  </si>
+  <si>
+    <t>HKCV-700T</t>
+  </si>
+  <si>
+    <t>210408a3da14fd0d</t>
+  </si>
+  <si>
+    <t>Cử Hàng Phương Thịnh</t>
+  </si>
+  <si>
+    <t>205/10 Huỳnh Minh Thạnh, Phước Bửu</t>
+  </si>
+  <si>
+    <t>0973.675.586</t>
+  </si>
+  <si>
+    <t>Máy hút khói kính cong CV-3570S</t>
+  </si>
+  <si>
+    <t>HKCV-3570S</t>
+  </si>
+  <si>
+    <t>210408f32b60298d</t>
+  </si>
+  <si>
+    <t>Công ty CP Vicken Việt Nam (Tình Phát)</t>
+  </si>
+  <si>
+    <t>P. Mỹ Xuân, TX Phú Mỹ, Bà Rịa Vũng Tàu</t>
+  </si>
+  <si>
+    <t>0904.959.319</t>
+  </si>
+  <si>
+    <t>210408984d107bd8</t>
+  </si>
+  <si>
+    <t>Nội Thất Hưng Thịnh Tây Ninh</t>
+  </si>
+  <si>
+    <t>587 Tôn Đức Thắng</t>
+  </si>
+  <si>
+    <t>0981.034.565</t>
+  </si>
+  <si>
+    <t>21040884360a8f47</t>
+  </si>
+  <si>
+    <t>20-10-2022</t>
+  </si>
+  <si>
+    <t>19-10-2024</t>
+  </si>
+  <si>
+    <t>A Thi - NT Mộc Việt Bình Dương</t>
+  </si>
+  <si>
+    <t>P. Định Hòa, Tp Thủ Dầu 1, Bình Dương</t>
+  </si>
+  <si>
+    <t>'0975535232</t>
+  </si>
+  <si>
+    <t>210408e2de0e1a1a</t>
+  </si>
+  <si>
+    <t>Điện Máy Minh Hạnh (BD)</t>
+  </si>
+  <si>
+    <t>Chợ An Cơ , Đường Lê Thị Trung , P An Phú , TP Thuận An , T Bình Dương</t>
+  </si>
+  <si>
+    <t>0974.910.102</t>
+  </si>
+  <si>
+    <t>210408f7d5395732</t>
+  </si>
+  <si>
+    <t>Cửa hàng Thanh Thảo</t>
+  </si>
+  <si>
+    <t>Ô1, Lô D, Đơờng BH24, P. Bình Hòa, TA, BD</t>
+  </si>
+  <si>
+    <t>0868505855</t>
+  </si>
+  <si>
+    <t>210408364e6ca492</t>
+  </si>
+  <si>
+    <t>2104087fb60d5856</t>
+  </si>
+  <si>
+    <t>Cty CN Môi Trường Nhật Hưng</t>
+  </si>
+  <si>
+    <t>268 QL 1K, Linh Xuân, TP Thủ Đức</t>
+  </si>
+  <si>
+    <t>0901464262</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ CV-626</t>
+  </si>
+  <si>
+    <t>BĐTCV-626</t>
+  </si>
+  <si>
+    <t>21040857cf3b7e28</t>
+  </si>
+  <si>
+    <t>Đại Lý Trường Boss</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>2104087860809ba9</t>
+  </si>
+  <si>
+    <t>TBVS VĂN TOÀN AMERICAN HOME</t>
+  </si>
+  <si>
+    <t>58 Lê Thị Hồng</t>
+  </si>
+  <si>
+    <t>0932.737.186</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ 1 hồng ngoại CA-9999</t>
+  </si>
+  <si>
+    <t>BĐTHN-9999</t>
+  </si>
+  <si>
+    <t>2104089b4bbc53d4</t>
+  </si>
+  <si>
+    <t>Vlxd Hoa Long Lâm Đồng</t>
+  </si>
+  <si>
+    <t>136 Huỳnh Thúc Kháng, P2, Bảo Lộc, Lâm Đồng</t>
+  </si>
+  <si>
+    <t>0913.626.315</t>
+  </si>
+  <si>
+    <t>Hút khói Canaval CA-8890S</t>
+  </si>
+  <si>
+    <t>HKCA-8890S</t>
+  </si>
+  <si>
+    <t>210408d13708b0ea</t>
+  </si>
+  <si>
+    <t>Công ty TNHH TM DV Nguyễn Thắng - Ngọc Thắm</t>
+  </si>
+  <si>
+    <t>498 Tân Thành</t>
+  </si>
+  <si>
+    <t>0987.658.283 - 0984.</t>
+  </si>
+  <si>
+    <t>210408ec50039ad9</t>
+  </si>
+  <si>
+    <t>Nội Thất Ý Tưởng Trẻ</t>
+  </si>
+  <si>
+    <t>0918.540.914</t>
+  </si>
+  <si>
+    <t>Bếp điện 1 từ 1 hồng ngoại CV-676</t>
+  </si>
+  <si>
+    <t>BĐTHNCV-676</t>
+  </si>
+  <si>
+    <t>210408ad7b7b6469</t>
+  </si>
+  <si>
+    <t>Showroom Ân Hưng Phát</t>
+  </si>
+  <si>
+    <t>44A Nguyễn Đình Chiểu</t>
+  </si>
+  <si>
+    <t>0978.659.898</t>
+  </si>
+  <si>
+    <t>210408996899231b</t>
+  </si>
+  <si>
+    <t>2104085783b483d6</t>
+  </si>
+  <si>
+    <t>2104088336de793d</t>
+  </si>
+  <si>
+    <t>Cửa hàng Thanh Bình 3 Biên Hòa</t>
+  </si>
+  <si>
+    <t>33 Đồng Khởi, Tân Mai, Biên Hòa, Đồng Nai</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ CV-879</t>
+  </si>
+  <si>
+    <t>BĐTCV-879</t>
+  </si>
+  <si>
+    <t>21040865179fdd7b</t>
+  </si>
+  <si>
+    <t>Bếp Thanh Sơn Đắk Nông</t>
+  </si>
+  <si>
+    <t>236 Tôn Đức Thắng</t>
+  </si>
+  <si>
+    <t>0825.823.825</t>
+  </si>
+  <si>
+    <t>21040856d2d96331</t>
+  </si>
+  <si>
+    <t>210408630fd96ca1</t>
+  </si>
+  <si>
+    <t>210408bab0c9d2f2</t>
+  </si>
+  <si>
+    <t>2104086bec695c2c</t>
+  </si>
+  <si>
+    <t>Nội Thất Đức Tín</t>
+  </si>
+  <si>
+    <t>24 Nguyễn Minh Trường</t>
+  </si>
+  <si>
+    <t>0787.826.262</t>
+  </si>
+  <si>
+    <t>210408f4dce32a5d</t>
+  </si>
+  <si>
+    <t>Anh Thạch Q12 - Cty Toàn Minh Tâm</t>
+  </si>
+  <si>
+    <t>0903306785</t>
+  </si>
+  <si>
+    <t>210408383a66f4d9</t>
+  </si>
+  <si>
+    <t>21040898c8cb146a</t>
+  </si>
+  <si>
+    <t>21040800437674cb</t>
+  </si>
+  <si>
+    <t>'Điện Nước Gia Khang (HM)</t>
+  </si>
+  <si>
+    <t>'16/5 Phan Văn Hớn, Ấp Nam Lân, Bà Điểm Hóc Môn</t>
+  </si>
+  <si>
+    <t>'0919933211</t>
+  </si>
+  <si>
+    <t>Hút khói Civina CV-3388A</t>
+  </si>
+  <si>
+    <t>HKCV-3388A</t>
+  </si>
+  <si>
+    <t>210408ca0fe5770a</t>
+  </si>
+  <si>
+    <t>2104081d175db654</t>
+  </si>
+  <si>
+    <t>Nội Thất Giá Rẻ Phan Rang</t>
+  </si>
+  <si>
+    <t>Mỹ trường 2 Nhơn Hải ninh Hải  Ninh Thuận</t>
+  </si>
+  <si>
+    <t>0798524412</t>
+  </si>
+  <si>
+    <t>21040865b060ab89</t>
+  </si>
+  <si>
+    <t>Sản Xuất Thiết Kế Thi Công NT Cao Cấp BP</t>
+  </si>
+  <si>
+    <t>Thôn tân Lực, Xã Bù Nho</t>
+  </si>
+  <si>
+    <t>0932.060.457</t>
+  </si>
+  <si>
+    <t>Hút khói  Civina CV-700B</t>
+  </si>
+  <si>
+    <t>HKCV-700B</t>
+  </si>
+  <si>
+    <t>210408605adef9ca</t>
+  </si>
+  <si>
+    <t>CH Thanh Thủy Kiến Tường L.A</t>
+  </si>
+  <si>
+    <t>Kiến Tường, Long An</t>
+  </si>
+  <si>
+    <t>0915.992.778</t>
+  </si>
+  <si>
+    <t>2104080016dbe1c0</t>
+  </si>
+  <si>
+    <t>2104081e9f7af0d4</t>
+  </si>
+  <si>
+    <t>NỘI THẤT NHỰA THUẬN PHÁT</t>
+  </si>
+  <si>
+    <t>0971.266.252</t>
+  </si>
+  <si>
+    <t>Hút khói Canaval CA-8290</t>
+  </si>
+  <si>
+    <t>HKCA-8290</t>
+  </si>
+  <si>
+    <t>210408e71ecb2c99</t>
+  </si>
+  <si>
+    <t>2104080ee9b67e55</t>
+  </si>
+  <si>
+    <t>210408ef1811c428</t>
+  </si>
+  <si>
+    <t>21040815d38c9bfa</t>
+  </si>
+  <si>
+    <t>2104084c121ce816</t>
+  </si>
+  <si>
+    <t>2104084b8cba5a6a</t>
+  </si>
+  <si>
+    <t>Vlxd Tiến Ngĩa Long An</t>
+  </si>
+  <si>
+    <t>QL 50 Cần Đước</t>
+  </si>
+  <si>
+    <t>2104085bad7083fc</t>
+  </si>
+  <si>
+    <t>06-06-2024</t>
+  </si>
+  <si>
+    <t>06-06-2026</t>
+  </si>
+  <si>
+    <t>Kích Hoạt</t>
+  </si>
+  <si>
+    <t>210408087d77fdcd</t>
+  </si>
+  <si>
+    <t>21040815da14a825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nội thất nhựa Linh Hân </t>
+  </si>
+  <si>
+    <t>21040850483e3366</t>
+  </si>
+  <si>
+    <t>210408e703ae3ee6</t>
+  </si>
+  <si>
+    <t>Thủy Nội Thất Tâm Đan Long An</t>
+  </si>
+  <si>
+    <t>Khu phố 4, Thị trấn Đức Hòa, Long An</t>
+  </si>
+  <si>
+    <t>0907414893</t>
+  </si>
+  <si>
+    <t>210408c5ce6e594c</t>
+  </si>
+  <si>
+    <t>Quốc Anh AV Horse Hóc Môn</t>
+  </si>
+  <si>
+    <t>210408237f688124</t>
+  </si>
+  <si>
+    <t>Bếp âm Civina  CV-828</t>
+  </si>
+  <si>
+    <t>BACV-828</t>
+  </si>
+  <si>
+    <t>21040883767733c1</t>
+  </si>
+  <si>
+    <t>210408e086bb21fa</t>
+  </si>
+  <si>
+    <t>210408de97fffee0</t>
+  </si>
+  <si>
+    <t>Phát Thành Đạt Nhơn TRạch</t>
+  </si>
+  <si>
+    <t>0983433378</t>
+  </si>
+  <si>
+    <t>2104082acc163cbd</t>
+  </si>
+  <si>
+    <t>ĐIỆN MÁY ĐẠI NGHĨA</t>
+  </si>
+  <si>
+    <t>Ấp 3, Xã Minh Lập</t>
+  </si>
+  <si>
+    <t>0937.831.970</t>
+  </si>
+  <si>
+    <t>2104088c438448ac</t>
+  </si>
+  <si>
+    <t>NT Gia Phú</t>
+  </si>
+  <si>
+    <t>Đường 19/4 , P.Xuân An</t>
+  </si>
+  <si>
+    <t>0901540999</t>
+  </si>
+  <si>
+    <t>210408940085841f</t>
+  </si>
+  <si>
+    <t>Cửa hàng VLXD Nhất Khang</t>
+  </si>
+  <si>
+    <t>Ngã 3 cảng Phước Hạnh KP Phước Lộc P. Tân Phước TX Phú Mỹ BRVT</t>
+  </si>
+  <si>
+    <t>0706772772</t>
+  </si>
+  <si>
+    <t>Bếp âm Canaval CA-6828</t>
+  </si>
+  <si>
+    <t>BACA-6828</t>
+  </si>
+  <si>
+    <t>2104083b73193d0c</t>
+  </si>
+  <si>
+    <t>Cửa hàng Tiến Minh</t>
+  </si>
+  <si>
+    <t>39 Nguyễn Văn Cừ, TP Phan Rang, Tỉnh Ninh Thuận</t>
+  </si>
+  <si>
+    <t>0912.344.575</t>
+  </si>
+  <si>
+    <t>210408ac8ca388e6</t>
+  </si>
+  <si>
+    <t>Vlxd Trọng Tín Bình Chánh</t>
+  </si>
+  <si>
+    <t>Đường Đinh Đức Thiện</t>
+  </si>
+  <si>
+    <t>0918249766</t>
+  </si>
+  <si>
+    <t>Bếp âm Civina CV-888</t>
+  </si>
+  <si>
+    <t>BACV-888</t>
+  </si>
+  <si>
+    <t>210408cf4147d02a</t>
+  </si>
+  <si>
+    <t>Cộng tác viên Thành Việt úc</t>
+  </si>
+  <si>
+    <t>109 Đặng Thúc Vịnh, Hóc Môn</t>
+  </si>
+  <si>
+    <t>0902.631.456</t>
+  </si>
+  <si>
+    <t>210408f7fbfe54ba</t>
+  </si>
+  <si>
+    <t>Showroom Phú Khang HM</t>
+  </si>
+  <si>
+    <t>6/4F Đỗ Văn Dậy, Hóc Môn</t>
+  </si>
+  <si>
+    <t>0975.111.800</t>
+  </si>
+  <si>
+    <t>21040850a0f503ec</t>
+  </si>
+  <si>
+    <t>21040852144b0955</t>
+  </si>
+  <si>
+    <t>210408f2b4c4325c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPP Điện Nước Bang Thương Mại </t>
+  </si>
+  <si>
+    <t>111 Nguyễn Chí Thanh. Thị Trấn Quảng Phú, H. Cư MAR, T. Đăk Lăk</t>
+  </si>
+  <si>
+    <t>0982.112.834</t>
+  </si>
+  <si>
+    <t>21040817b1e5ffec</t>
+  </si>
+  <si>
+    <t>Showroom Âu Việt - Bình Dương</t>
+  </si>
+  <si>
+    <t>246 GS1 Khu Phố Nhị Đồng 2</t>
+  </si>
+  <si>
+    <t>0964267186</t>
+  </si>
+  <si>
+    <t>2104085dc6cc74b9</t>
+  </si>
+  <si>
+    <t>NT NGUYỄN XUÂN TÌNH</t>
+  </si>
+  <si>
+    <t>17 Trần Bội Cơ, P.Iaking, TP Pleiku, Gia Lai</t>
+  </si>
+  <si>
+    <t>0915494078</t>
+  </si>
+  <si>
+    <t>Bếp âm Canaval CA-6838</t>
+  </si>
+  <si>
+    <t>BACA-6838</t>
+  </si>
+  <si>
+    <t>210408d5ff4dda38</t>
+  </si>
+  <si>
+    <t>Hút khói Canaval CA-8700G</t>
+  </si>
+  <si>
+    <t>HKCA-8700G</t>
+  </si>
+  <si>
+    <t>210408d9a40341e3</t>
+  </si>
+  <si>
+    <t>210408765d4debba</t>
+  </si>
+  <si>
+    <t>21040852c1575bde</t>
+  </si>
+  <si>
+    <t>210408202a9515bb</t>
+  </si>
+  <si>
+    <t>Công ty Flash Home (GV)</t>
+  </si>
+  <si>
+    <t>202 Lê Văn Thọ, P11, Gò Vấp</t>
+  </si>
+  <si>
+    <t>0975.720.431</t>
+  </si>
+  <si>
+    <t>2104087f162a0dfa</t>
+  </si>
+  <si>
+    <t>210408a1649038e7</t>
+  </si>
+  <si>
+    <t>Showroom Quý Dũng BP</t>
+  </si>
+  <si>
+    <t>Chợ đội 8, Thôn 2</t>
+  </si>
+  <si>
+    <t>03.4444.9500 - 0966.</t>
+  </si>
+  <si>
+    <t>210408e52a4357e3</t>
+  </si>
+  <si>
+    <t>210408eaa623a453</t>
+  </si>
+  <si>
+    <t>28-06-2024</t>
+  </si>
+  <si>
+    <t>28-06-2026</t>
+  </si>
+  <si>
+    <t>2104084b1c3936a8</t>
+  </si>
+  <si>
+    <t>Chị Loan TBVS Tora</t>
+  </si>
+  <si>
+    <t>0935.805.303</t>
+  </si>
+  <si>
+    <t>210408915bca0822</t>
+  </si>
+  <si>
+    <t>21040823c3ee45ce</t>
+  </si>
+  <si>
+    <t>VLXD Quỳnh An (Cần Thơ)</t>
+  </si>
+  <si>
+    <t>A30 Nguyễn Văn Cừ, P.An Hòa, Q.Ninh Kiều, Cần Thơ</t>
+  </si>
+  <si>
+    <t>0919.909.879</t>
+  </si>
+  <si>
+    <t>210408a81f525a3c</t>
+  </si>
+  <si>
+    <t>Nội Thất Nguyễn Minh</t>
+  </si>
+  <si>
+    <t>421/4/12 Kha Vạn Cân</t>
+  </si>
+  <si>
+    <t>0935.526.880</t>
+  </si>
+  <si>
+    <t>21040844835e5d27</t>
+  </si>
+  <si>
+    <t>Bếp âm Canaval CA-6888</t>
+  </si>
+  <si>
+    <t>BACA-6888</t>
+  </si>
+  <si>
+    <t>210408868cb457c8</t>
+  </si>
+  <si>
+    <t>2104084738980aa0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nội Thất Bách Phát </t>
+  </si>
+  <si>
+    <t>616/79 Lê Trọng Tấn</t>
+  </si>
+  <si>
+    <t>0983.976.677</t>
+  </si>
+  <si>
+    <t>Bếp điên từ hồng ngoại CIVIN CV-690</t>
+  </si>
+  <si>
+    <t>BĐTHNCV-690</t>
+  </si>
+  <si>
+    <t>2104089fd7622b15</t>
+  </si>
+  <si>
+    <t>CTY TNHH TMDV CẨM ANH Q6</t>
+  </si>
+  <si>
+    <t>61 Ngô Nhân Tịnh, Quận 6</t>
+  </si>
+  <si>
+    <t>0976.925.186</t>
+  </si>
+  <si>
+    <t>210408772f5cc6ad</t>
+  </si>
+  <si>
+    <t>Siêu Thị Bếp Đại Việt (LĐ)</t>
+  </si>
+  <si>
+    <t>196 Ngô Quyền, P6, TP Đà Lạt, T Lâm Đồng</t>
+  </si>
+  <si>
+    <t>0397.361.955</t>
+  </si>
+  <si>
+    <t>210408a75b050fa4</t>
+  </si>
+  <si>
+    <t>21040835fa152b7e</t>
+  </si>
+  <si>
+    <t>VLXD Vinh Hạnh</t>
+  </si>
+  <si>
+    <t>Ấp 5</t>
+  </si>
+  <si>
+    <t>210408c66086b670</t>
+  </si>
+  <si>
+    <t>VLXD Anh Bửu 2</t>
+  </si>
+  <si>
+    <t>Ấp Muôn Nghiệp, Xã Bình Đông, Thị Xã Gò Công, Tiền Giang</t>
+  </si>
+  <si>
+    <t>0919.817.281</t>
+  </si>
+  <si>
+    <t>Bếp điện từ CV-629</t>
+  </si>
+  <si>
+    <t>BĐTCV-629</t>
+  </si>
+  <si>
+    <t>21040873b17a16af</t>
+  </si>
+  <si>
+    <t>VLXD Hoa Long (ĐN)</t>
+  </si>
+  <si>
+    <t>DT768, Ấp 2, X Thạnh Phú, H Vĩnh Cửu, T Đồng Nai</t>
+  </si>
+  <si>
+    <t>0974.624.910 / 0915.</t>
+  </si>
+  <si>
+    <t>Bếp điện 1 từ 1 hồng ngoại CV656</t>
+  </si>
+  <si>
+    <t>BĐTHNCV-656</t>
+  </si>
+  <si>
+    <t>210408ecbf1264de</t>
+  </si>
+  <si>
+    <t>Quang Minh Home</t>
+  </si>
+  <si>
+    <t>1/135A Tổ 1, KP Hòa Lân, P.Thuận Giao, TP.Thuận An</t>
+  </si>
+  <si>
+    <t>0918-064-585 A.Bình</t>
+  </si>
+  <si>
+    <t>21040800ec189b2c</t>
+  </si>
+  <si>
+    <t>2104086863eea7bb</t>
+  </si>
+  <si>
+    <t>21040868af6aba82</t>
+  </si>
+  <si>
+    <t>210408777ff4a326</t>
+  </si>
+  <si>
+    <t>ĐIỆN MÁY BUÔN PHƯƠNG CẦN THƠ</t>
+  </si>
+  <si>
+    <t>20 Lê Thánh Tôn</t>
+  </si>
+  <si>
+    <t>0939.454.999</t>
+  </si>
+  <si>
+    <t>2104083235c4eeb6</t>
+  </si>
+  <si>
+    <t>210408862329f5df</t>
+  </si>
+  <si>
+    <t>Cửa hàng Minh Hùng</t>
+  </si>
+  <si>
+    <t>522 Hơơng lộ 2, P Bình Trị Đông, Bình Tân</t>
+  </si>
+  <si>
+    <t>0919.175.407</t>
+  </si>
+  <si>
+    <t>Bếp điện 1 từ 1 hồng ngoại CA9928</t>
+  </si>
+  <si>
+    <t>BĐTHNCA-9928</t>
+  </si>
+  <si>
+    <t>210408e67ac6ec05</t>
+  </si>
+  <si>
+    <t>21040869f62c756e</t>
+  </si>
+  <si>
+    <t>DDIENJ MÁY LÃM PHƯỢNG</t>
+  </si>
+  <si>
+    <t>KHÓM 1</t>
+  </si>
+  <si>
+    <t>0939.995.553</t>
+  </si>
+  <si>
+    <t>210408f0e003dcb4</t>
+  </si>
+  <si>
+    <t>210408617efcf337</t>
+  </si>
+  <si>
+    <t>210408ec5a8c2d9b</t>
+  </si>
+  <si>
+    <t>210408bf4b3fd0c3</t>
+  </si>
+  <si>
+    <t>NT HUY PHÁT (Q9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> '709A ĐỖ XUÂN HỢP, P PHÚ HỮU, TP THỦ ĐỨC</t>
+  </si>
+  <si>
+    <t>'0974.480.935</t>
+  </si>
+  <si>
+    <t>Hút khói  Civina CV-700D</t>
+  </si>
+  <si>
+    <t>HKCV-700D</t>
+  </si>
+  <si>
+    <t>210408a95d978a40</t>
+  </si>
+  <si>
+    <t>CH Quang Huy TPhú</t>
+  </si>
+  <si>
+    <t>345A Lê Trọng Tấn, P.Sơn Kỳ</t>
+  </si>
+  <si>
+    <t>0915756465</t>
+  </si>
+  <si>
+    <t>210408449a37afd4</t>
+  </si>
+  <si>
+    <t>Cửa Hàng Liễu Tới</t>
+  </si>
+  <si>
+    <t>TT Chư Sê</t>
+  </si>
+  <si>
+    <t>0966.229.922</t>
+  </si>
+  <si>
+    <t>210408ab58c42915</t>
+  </si>
+  <si>
+    <t>ANH VINH (TÂN PHÚ)</t>
+  </si>
+  <si>
+    <t>196 Tân Kì Tân Quý, P.Tân Sơn Nhì, Tân Phú</t>
+  </si>
+  <si>
+    <t>0932.639.859</t>
+  </si>
+  <si>
+    <t>Hút khói  Civina CV-700A</t>
+  </si>
+  <si>
+    <t>HKCV-700A</t>
+  </si>
+  <si>
+    <t>210408ccb7d2a96c</t>
+  </si>
+  <si>
+    <t>05-06-2024</t>
+  </si>
+  <si>
+    <t>05-06-2026</t>
+  </si>
+  <si>
+    <t>Cửa hàng Hoàng Tuấn (Tiền Giang)</t>
+  </si>
+  <si>
+    <t>90 Trần Ngọc Giải, P.6, Tp.Mỹ Tho, Tiền Giang</t>
+  </si>
+  <si>
+    <t>0934.527.126 A.Hiếu</t>
+  </si>
+  <si>
+    <t>210408415c14ecf0</t>
+  </si>
+  <si>
+    <t>NỘI THẤT HĐ DESIGNE</t>
+  </si>
+  <si>
+    <t>293/1/27A Nguyễn Thị Minh Khai, Phường Phú Hòa</t>
+  </si>
+  <si>
+    <t>0962.739.135</t>
+  </si>
+  <si>
+    <t>Hút khói  Canaval CA-8770S</t>
+  </si>
+  <si>
+    <t>HKCA-8770S</t>
+  </si>
+  <si>
+    <t>210408f015822ee1</t>
+  </si>
+  <si>
+    <t>210408bdeb39072c</t>
+  </si>
+  <si>
+    <t>Máy hút khói CIVIN SMART</t>
+  </si>
+  <si>
+    <t>HKCV-Smart</t>
+  </si>
+  <si>
+    <t>210408d842908c23</t>
+  </si>
+  <si>
+    <t>210408a773db6cb8</t>
+  </si>
+  <si>
+    <t>210408f1e9a86c2e</t>
+  </si>
+  <si>
+    <t>Máy hút khói âm tủ Canaval CA-8700T</t>
+  </si>
+  <si>
+    <t>HKCA-8700T</t>
+  </si>
+  <si>
+    <t>210408c72f4e65d1</t>
+  </si>
+  <si>
+    <t>Máy hút khói kính cong CV-3270S</t>
+  </si>
+  <si>
+    <t>HKCV-3270S</t>
+  </si>
+  <si>
+    <t>21040817bc4d58d9</t>
+  </si>
+  <si>
+    <t>210408526e0bc445</t>
+  </si>
+  <si>
+    <t>210408720ab1df43</t>
+  </si>
+  <si>
+    <t>Công ty TNHH Mộc Gia Sài Gòn</t>
+  </si>
+  <si>
+    <t>84 Đơờng số 16, KP3, P. Hiệp Bình Chánh, TĐ</t>
+  </si>
+  <si>
+    <t>0909634467</t>
+  </si>
+  <si>
+    <t>210408298f71ce67</t>
+  </si>
+  <si>
+    <t>Cửa hàng Thành Tốt</t>
+  </si>
+  <si>
+    <t>212 Đơờng Dơơng Thị Mơời, KP3, P.TCH, Q12</t>
+  </si>
+  <si>
+    <t>0938.018.468</t>
+  </si>
+  <si>
+    <t>Hút khói Canaval CA-8700S</t>
+  </si>
+  <si>
+    <t>HKCA-8700S</t>
+  </si>
+  <si>
+    <t>23ji30az</t>
+  </si>
+  <si>
+    <t>23jsjw48</t>
+  </si>
+  <si>
+    <t>VLXD LINH TRUNG</t>
+  </si>
+  <si>
+    <t>265B Thôn 3, Nam Chính</t>
+  </si>
+  <si>
+    <t>0911.456.173</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ CA-9919</t>
+  </si>
+  <si>
+    <t>BĐTCA-9919</t>
+  </si>
+  <si>
+    <t>23qlydu3</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ CV-616</t>
+  </si>
+  <si>
+    <t>BĐTCV-616</t>
+  </si>
+  <si>
+    <t>23d6btxh</t>
+  </si>
+  <si>
+    <t>VLXD Xuân Lý</t>
+  </si>
+  <si>
+    <t>Xã Hiệp Thành</t>
+  </si>
+  <si>
+    <t>0918593386</t>
+  </si>
+  <si>
+    <t>Máy hút khói CANAVAL CA-8270</t>
+  </si>
+  <si>
+    <t>HKCA-8270</t>
+  </si>
+  <si>
+    <t>23crpr6n</t>
+  </si>
+  <si>
+    <t>VLXD Đức Tài Phát</t>
+  </si>
+  <si>
+    <t>0989.139.283</t>
+  </si>
+  <si>
+    <t>23jmiu68</t>
+  </si>
+  <si>
+    <t>23cz3u4b</t>
+  </si>
+  <si>
+    <t>Nội Thất Nhựa Phú Hào</t>
+  </si>
+  <si>
+    <t>463 Hà Huy Tập</t>
+  </si>
+  <si>
+    <t>0902.075.533</t>
+  </si>
+  <si>
+    <t>233q3mq9</t>
+  </si>
+  <si>
+    <t>23d2zdnn</t>
+  </si>
+  <si>
+    <t>23rj7b4q</t>
+  </si>
+  <si>
+    <t>Bếp điện 1 từ 1 hồng ngoại CA-9929</t>
+  </si>
+  <si>
+    <t>BĐTHNCA-9929</t>
+  </si>
+  <si>
+    <t>23dlga7p</t>
+  </si>
+  <si>
+    <t>23jetc4s</t>
+  </si>
+  <si>
+    <t>Bếp điện 2 từ CA-9969</t>
+  </si>
+  <si>
+    <t>BĐTCA-9969</t>
+  </si>
+  <si>
+    <t>23rqz99p</t>
+  </si>
+  <si>
+    <t>23cx0s58</t>
+  </si>
+  <si>
+    <t>Công ty CPXD &amp; BĐS Home Land</t>
+  </si>
+  <si>
+    <t>1390 Phú Riềng Đỏ, Đồng Xoài, Bình Phơớc</t>
+  </si>
+  <si>
+    <t>0988.868.876</t>
+  </si>
+  <si>
+    <t>23dbnb8r</t>
+  </si>
+  <si>
+    <t>23csuogn</t>
+  </si>
+  <si>
+    <t>238q5br8</t>
+  </si>
+  <si>
+    <t>CÔNG TY HOÀNG LINH BC</t>
+  </si>
+  <si>
+    <t>B2/3B Đường Liên Ấp 2-6, Vĩnh Lộc A</t>
+  </si>
+  <si>
+    <t>0985.682.008</t>
+  </si>
+  <si>
+    <t>Hút khói Civina CV-600T</t>
+  </si>
+  <si>
+    <t>HKCV-600T</t>
+  </si>
+  <si>
+    <t>235h7kls</t>
+  </si>
+  <si>
+    <t>23ny846m</t>
+  </si>
+  <si>
+    <t>Đại Lý Hồng Gấm</t>
+  </si>
+  <si>
+    <t>0352.776.726</t>
+  </si>
+  <si>
+    <t>23kza56n</t>
+  </si>
+  <si>
+    <t>23nj9vul</t>
+  </si>
+  <si>
+    <t>23lv5lin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLXD THiên Lộc Phát </t>
+  </si>
+  <si>
+    <t>36/17 Tổ 6 ấp 7, Xuân Thới Thượng, Hóc Môn</t>
+  </si>
+  <si>
+    <t>0901.383.435</t>
+  </si>
+  <si>
+    <t>23dng1wy</t>
+  </si>
+  <si>
+    <t>21-06-2024</t>
+  </si>
+  <si>
+    <t>21-06-2026</t>
+  </si>
+  <si>
+    <t>VLXD Điểm Ngọc - (Chị Cẩm)</t>
+  </si>
+  <si>
+    <t>Phạm Hùng, P9, TP Vĩnh Long</t>
+  </si>
+  <si>
+    <t>0908.229.278</t>
+  </si>
+  <si>
+    <t>23jfq8f2</t>
+  </si>
+  <si>
+    <t>235ox5bg</t>
+  </si>
+  <si>
+    <t>Trung tâm Pha Màu Minh Hiền</t>
+  </si>
+  <si>
+    <t>55 Nguyễn Tất Thành</t>
+  </si>
+  <si>
+    <t>0902.433.345</t>
+  </si>
+  <si>
+    <t>23c3qc2a</t>
+  </si>
+  <si>
+    <t>23cl4r58</t>
+  </si>
+  <si>
+    <t>Bếp Hồ Tuấn Linh</t>
+  </si>
+  <si>
+    <t>0362162211</t>
+  </si>
+  <si>
+    <t>23rdkudk</t>
+  </si>
+  <si>
+    <t>23d6te6r</t>
+  </si>
+  <si>
+    <t>23ce7u6v</t>
+  </si>
+  <si>
+    <t>23dhwjlx</t>
+  </si>
+  <si>
+    <t>23ru10o7</t>
+  </si>
+  <si>
+    <t>23qgq6yb</t>
+  </si>
+  <si>
+    <t>23jlsa4m</t>
+  </si>
+  <si>
+    <t>Nội Thất Vân Khoa</t>
+  </si>
+  <si>
+    <t>DDT Lộc An</t>
+  </si>
+  <si>
+    <t>0938.766.090</t>
+  </si>
+  <si>
+    <t>23lrml54</t>
+  </si>
+  <si>
+    <t>23dn5h0s</t>
+  </si>
+  <si>
+    <t>Nội thất Thông Loan</t>
+  </si>
+  <si>
+    <t>Hùng Vương, TT. Mỹ AN</t>
+  </si>
+  <si>
+    <t>0907.881.918</t>
+  </si>
+  <si>
+    <t>23rbx9x8</t>
+  </si>
+  <si>
+    <t>23btj2r2</t>
+  </si>
+  <si>
+    <t>Nội Thất Kiến Trúc An Tâm</t>
+  </si>
+  <si>
+    <t>S2.08 Vinhome Ocean Park, Đại Dương, Đa Tốn</t>
+  </si>
+  <si>
+    <t>0962.836.338</t>
+  </si>
+  <si>
+    <t>2357io1k</t>
   </si>
 </sst>
 </file>
@@ -380,16 +1727,16 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="17" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="51" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="83" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="6" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="9" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="42" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="15" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="19" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="23" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="26" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="23" bestFit="true" customWidth="true" style="0"/>
@@ -425,6 +1772,4770 @@
       </c>
       <c r="J1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21"/>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24"/>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" t="s">
+        <v>110</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27"/>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29"/>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" t="s">
+        <v>132</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" t="s">
+        <v>137</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36"/>
+      <c r="D36" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" t="s">
+        <v>143</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" t="s">
+        <v>131</v>
+      </c>
+      <c r="G39" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42"/>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" t="s">
+        <v>152</v>
+      </c>
+      <c r="J42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" t="s">
+        <v>154</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44"/>
+      <c r="D44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" t="s">
+        <v>155</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" t="s">
+        <v>157</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" t="s">
+        <v>131</v>
+      </c>
+      <c r="G46" t="s">
+        <v>158</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G47" t="s">
+        <v>162</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" t="s">
+        <v>164</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" t="s">
+        <v>166</v>
+      </c>
+      <c r="G49" t="s">
+        <v>167</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G50" t="s">
+        <v>168</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" t="s">
+        <v>169</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52"/>
+      <c r="D52" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F52" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" t="s">
+        <v>172</v>
+      </c>
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" t="s">
+        <v>165</v>
+      </c>
+      <c r="F53" t="s">
+        <v>166</v>
+      </c>
+      <c r="G53" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" t="s">
+        <v>165</v>
+      </c>
+      <c r="F54" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" t="s">
+        <v>185</v>
+      </c>
+      <c r="G55" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C56" t="s">
+        <v>188</v>
+      </c>
+      <c r="D56" t="s">
+        <v>189</v>
+      </c>
+      <c r="E56" t="s">
+        <v>184</v>
+      </c>
+      <c r="F56" t="s">
+        <v>185</v>
+      </c>
+      <c r="G56" t="s">
+        <v>190</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>191</v>
+      </c>
+      <c r="C57" t="s">
+        <v>192</v>
+      </c>
+      <c r="D57" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" t="s">
+        <v>195</v>
+      </c>
+      <c r="G57" t="s">
+        <v>196</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" t="s">
+        <v>198</v>
+      </c>
+      <c r="D58" t="s">
+        <v>199</v>
+      </c>
+      <c r="E58" t="s">
+        <v>194</v>
+      </c>
+      <c r="F58" t="s">
+        <v>195</v>
+      </c>
+      <c r="G58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" t="s">
+        <v>202</v>
+      </c>
+      <c r="D59" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" t="s">
+        <v>184</v>
+      </c>
+      <c r="F59" t="s">
+        <v>185</v>
+      </c>
+      <c r="G59" t="s">
+        <v>204</v>
+      </c>
+      <c r="H59" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>181</v>
+      </c>
+      <c r="C60" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" t="s">
+        <v>183</v>
+      </c>
+      <c r="E60" t="s">
+        <v>184</v>
+      </c>
+      <c r="F60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G60" t="s">
+        <v>205</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" t="s">
+        <v>184</v>
+      </c>
+      <c r="F61" t="s">
+        <v>185</v>
+      </c>
+      <c r="G61" t="s">
+        <v>206</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" t="s">
+        <v>208</v>
+      </c>
+      <c r="D62" t="s">
+        <v>209</v>
+      </c>
+      <c r="E62" t="s">
+        <v>194</v>
+      </c>
+      <c r="F62" t="s">
+        <v>195</v>
+      </c>
+      <c r="G62" t="s">
+        <v>210</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>211</v>
+      </c>
+      <c r="C63" t="s">
+        <v>212</v>
+      </c>
+      <c r="D63" t="s">
+        <v>213</v>
+      </c>
+      <c r="E63" t="s">
+        <v>194</v>
+      </c>
+      <c r="F63" t="s">
+        <v>195</v>
+      </c>
+      <c r="G63" t="s">
+        <v>214</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>215</v>
+      </c>
+      <c r="C64" t="s">
+        <v>216</v>
+      </c>
+      <c r="D64" t="s">
+        <v>217</v>
+      </c>
+      <c r="E64" t="s">
+        <v>218</v>
+      </c>
+      <c r="F64" t="s">
+        <v>219</v>
+      </c>
+      <c r="G64" t="s">
+        <v>220</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65" t="s">
+        <v>221</v>
+      </c>
+      <c r="F65" t="s">
+        <v>222</v>
+      </c>
+      <c r="G65" t="s">
+        <v>223</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" t="s">
+        <v>221</v>
+      </c>
+      <c r="F66" t="s">
+        <v>222</v>
+      </c>
+      <c r="G66" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>163</v>
+      </c>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67" t="s">
+        <v>221</v>
+      </c>
+      <c r="F67" t="s">
+        <v>222</v>
+      </c>
+      <c r="G67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D68" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" t="s">
+        <v>218</v>
+      </c>
+      <c r="F68" t="s">
+        <v>219</v>
+      </c>
+      <c r="G68" t="s">
+        <v>226</v>
+      </c>
+      <c r="H68" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" t="s">
+        <v>229</v>
+      </c>
+      <c r="E69" t="s">
+        <v>221</v>
+      </c>
+      <c r="F69" t="s">
+        <v>222</v>
+      </c>
+      <c r="G69" t="s">
+        <v>230</v>
+      </c>
+      <c r="H69" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" t="s">
+        <v>47</v>
+      </c>
+      <c r="D70" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" t="s">
+        <v>221</v>
+      </c>
+      <c r="F70" t="s">
+        <v>222</v>
+      </c>
+      <c r="G70" t="s">
+        <v>231</v>
+      </c>
+      <c r="H70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>232</v>
+      </c>
+      <c r="C71" t="s">
+        <v>233</v>
+      </c>
+      <c r="D71" t="s">
+        <v>234</v>
+      </c>
+      <c r="E71" t="s">
+        <v>221</v>
+      </c>
+      <c r="F71" t="s">
+        <v>222</v>
+      </c>
+      <c r="G71" t="s">
+        <v>235</v>
+      </c>
+      <c r="H71" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>163</v>
+      </c>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72" t="s">
+        <v>221</v>
+      </c>
+      <c r="F72" t="s">
+        <v>222</v>
+      </c>
+      <c r="G72" t="s">
+        <v>236</v>
+      </c>
+      <c r="H72" t="s">
+        <v>237</v>
+      </c>
+      <c r="I72" t="s">
+        <v>238</v>
+      </c>
+      <c r="J72" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" t="s">
+        <v>47</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+      <c r="E73" t="s">
+        <v>221</v>
+      </c>
+      <c r="F73" t="s">
+        <v>222</v>
+      </c>
+      <c r="G73" t="s">
+        <v>239</v>
+      </c>
+      <c r="H73" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+      <c r="C74"/>
+      <c r="D74" t="s">
+        <v>241</v>
+      </c>
+      <c r="E74" t="s">
+        <v>221</v>
+      </c>
+      <c r="F74" t="s">
+        <v>222</v>
+      </c>
+      <c r="G74" t="s">
+        <v>242</v>
+      </c>
+      <c r="H74" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>227</v>
+      </c>
+      <c r="C75" t="s">
+        <v>228</v>
+      </c>
+      <c r="D75" t="s">
+        <v>229</v>
+      </c>
+      <c r="E75" t="s">
+        <v>221</v>
+      </c>
+      <c r="F75" t="s">
+        <v>222</v>
+      </c>
+      <c r="G75" t="s">
+        <v>243</v>
+      </c>
+      <c r="H75" t="s">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>244</v>
+      </c>
+      <c r="C76" t="s">
+        <v>245</v>
+      </c>
+      <c r="D76" t="s">
+        <v>246</v>
+      </c>
+      <c r="E76" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" t="s">
+        <v>72</v>
+      </c>
+      <c r="G76" t="s">
+        <v>247</v>
+      </c>
+      <c r="H76" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>248</v>
+      </c>
+      <c r="C77" t="s">
+        <v>249</v>
+      </c>
+      <c r="D77" t="s">
+        <v>250</v>
+      </c>
+      <c r="E77" t="s">
+        <v>221</v>
+      </c>
+      <c r="F77" t="s">
+        <v>222</v>
+      </c>
+      <c r="G77" t="s">
+        <v>251</v>
+      </c>
+      <c r="H77" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>197</v>
+      </c>
+      <c r="C78" t="s">
+        <v>198</v>
+      </c>
+      <c r="D78" t="s">
+        <v>199</v>
+      </c>
+      <c r="E78" t="s">
+        <v>252</v>
+      </c>
+      <c r="F78" t="s">
+        <v>253</v>
+      </c>
+      <c r="G78" t="s">
+        <v>254</v>
+      </c>
+      <c r="H78" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" t="s">
+        <v>75</v>
+      </c>
+      <c r="D79" t="s">
+        <v>76</v>
+      </c>
+      <c r="E79" t="s">
+        <v>252</v>
+      </c>
+      <c r="F79" t="s">
+        <v>253</v>
+      </c>
+      <c r="G79" t="s">
+        <v>255</v>
+      </c>
+      <c r="H79" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C80" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" t="s">
+        <v>258</v>
+      </c>
+      <c r="E80" t="s">
+        <v>259</v>
+      </c>
+      <c r="F80" t="s">
+        <v>260</v>
+      </c>
+      <c r="G80" t="s">
+        <v>261</v>
+      </c>
+      <c r="H80" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>262</v>
+      </c>
+      <c r="C81" t="s">
+        <v>263</v>
+      </c>
+      <c r="D81" t="s">
+        <v>264</v>
+      </c>
+      <c r="E81" t="s">
+        <v>259</v>
+      </c>
+      <c r="F81" t="s">
+        <v>260</v>
+      </c>
+      <c r="G81" t="s">
+        <v>265</v>
+      </c>
+      <c r="H81" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>266</v>
+      </c>
+      <c r="C82" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" t="s">
+        <v>268</v>
+      </c>
+      <c r="E82" t="s">
+        <v>259</v>
+      </c>
+      <c r="F82" t="s">
+        <v>260</v>
+      </c>
+      <c r="G82" t="s">
+        <v>269</v>
+      </c>
+      <c r="H82" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" t="s">
+        <v>267</v>
+      </c>
+      <c r="D83" t="s">
+        <v>268</v>
+      </c>
+      <c r="E83" t="s">
+        <v>259</v>
+      </c>
+      <c r="F83" t="s">
+        <v>260</v>
+      </c>
+      <c r="G83" t="s">
+        <v>270</v>
+      </c>
+      <c r="H83" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s">
+        <v>272</v>
+      </c>
+      <c r="D84"/>
+      <c r="E84" t="s">
+        <v>259</v>
+      </c>
+      <c r="F84" t="s">
+        <v>260</v>
+      </c>
+      <c r="G84" t="s">
+        <v>273</v>
+      </c>
+      <c r="H84" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>274</v>
+      </c>
+      <c r="C85" t="s">
+        <v>275</v>
+      </c>
+      <c r="D85" t="s">
+        <v>276</v>
+      </c>
+      <c r="E85" t="s">
+        <v>277</v>
+      </c>
+      <c r="F85" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" t="s">
+        <v>279</v>
+      </c>
+      <c r="H85" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>280</v>
+      </c>
+      <c r="C86" t="s">
+        <v>281</v>
+      </c>
+      <c r="D86" t="s">
+        <v>282</v>
+      </c>
+      <c r="E86" t="s">
+        <v>283</v>
+      </c>
+      <c r="F86" t="s">
+        <v>284</v>
+      </c>
+      <c r="G86" t="s">
+        <v>285</v>
+      </c>
+      <c r="H86" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>286</v>
+      </c>
+      <c r="C87" t="s">
+        <v>287</v>
+      </c>
+      <c r="D87" t="s">
+        <v>288</v>
+      </c>
+      <c r="E87" t="s">
+        <v>283</v>
+      </c>
+      <c r="F87" t="s">
+        <v>284</v>
+      </c>
+      <c r="G87" t="s">
+        <v>289</v>
+      </c>
+      <c r="H87" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>256</v>
+      </c>
+      <c r="C88" t="s">
+        <v>257</v>
+      </c>
+      <c r="D88" t="s">
+        <v>258</v>
+      </c>
+      <c r="E88" t="s">
+        <v>277</v>
+      </c>
+      <c r="F88" t="s">
+        <v>278</v>
+      </c>
+      <c r="G88" t="s">
+        <v>290</v>
+      </c>
+      <c r="H88" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" t="s">
+        <v>277</v>
+      </c>
+      <c r="F89" t="s">
+        <v>278</v>
+      </c>
+      <c r="G89" t="s">
+        <v>291</v>
+      </c>
+      <c r="H89" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>280</v>
+      </c>
+      <c r="C90" t="s">
+        <v>281</v>
+      </c>
+      <c r="D90" t="s">
+        <v>282</v>
+      </c>
+      <c r="E90" t="s">
+        <v>283</v>
+      </c>
+      <c r="F90" t="s">
+        <v>284</v>
+      </c>
+      <c r="G90" t="s">
+        <v>292</v>
+      </c>
+      <c r="H90" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>293</v>
+      </c>
+      <c r="C91" t="s">
+        <v>294</v>
+      </c>
+      <c r="D91" t="s">
+        <v>295</v>
+      </c>
+      <c r="E91" t="s">
+        <v>283</v>
+      </c>
+      <c r="F91" t="s">
+        <v>284</v>
+      </c>
+      <c r="G91" t="s">
+        <v>296</v>
+      </c>
+      <c r="H91" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" t="s">
+        <v>283</v>
+      </c>
+      <c r="F92" t="s">
+        <v>284</v>
+      </c>
+      <c r="G92" t="s">
+        <v>297</v>
+      </c>
+      <c r="H92" t="s">
+        <v>16</v>
+      </c>
+      <c r="I92" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>298</v>
+      </c>
+      <c r="C93" t="s">
+        <v>299</v>
+      </c>
+      <c r="D93" t="s">
+        <v>300</v>
+      </c>
+      <c r="E93" t="s">
+        <v>301</v>
+      </c>
+      <c r="F93" t="s">
+        <v>302</v>
+      </c>
+      <c r="G93" t="s">
+        <v>303</v>
+      </c>
+      <c r="H93" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94" t="s">
+        <v>301</v>
+      </c>
+      <c r="F94" t="s">
+        <v>302</v>
+      </c>
+      <c r="G94" t="s">
+        <v>304</v>
+      </c>
+      <c r="H94" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>305</v>
+      </c>
+      <c r="C95" t="s">
+        <v>306</v>
+      </c>
+      <c r="D95" t="s">
+        <v>307</v>
+      </c>
+      <c r="E95" t="s">
+        <v>301</v>
+      </c>
+      <c r="F95" t="s">
+        <v>302</v>
+      </c>
+      <c r="G95" t="s">
+        <v>308</v>
+      </c>
+      <c r="H95" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>54</v>
+      </c>
+      <c r="C96" t="s">
+        <v>55</v>
+      </c>
+      <c r="D96" t="s">
+        <v>56</v>
+      </c>
+      <c r="E96" t="s">
+        <v>71</v>
+      </c>
+      <c r="F96" t="s">
+        <v>72</v>
+      </c>
+      <c r="G96" t="s">
+        <v>309</v>
+      </c>
+      <c r="H96" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>197</v>
+      </c>
+      <c r="C97" t="s">
+        <v>198</v>
+      </c>
+      <c r="D97" t="s">
+        <v>199</v>
+      </c>
+      <c r="E97" t="s">
+        <v>71</v>
+      </c>
+      <c r="F97" t="s">
+        <v>72</v>
+      </c>
+      <c r="G97" t="s">
+        <v>310</v>
+      </c>
+      <c r="H97" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>197</v>
+      </c>
+      <c r="C98" t="s">
+        <v>198</v>
+      </c>
+      <c r="D98" t="s">
+        <v>199</v>
+      </c>
+      <c r="E98" t="s">
+        <v>71</v>
+      </c>
+      <c r="F98" t="s">
+        <v>72</v>
+      </c>
+      <c r="G98" t="s">
+        <v>311</v>
+      </c>
+      <c r="H98" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>312</v>
+      </c>
+      <c r="C99" t="s">
+        <v>313</v>
+      </c>
+      <c r="D99" t="s">
+        <v>314</v>
+      </c>
+      <c r="E99" t="s">
+        <v>315</v>
+      </c>
+      <c r="F99" t="s">
+        <v>316</v>
+      </c>
+      <c r="G99" t="s">
+        <v>317</v>
+      </c>
+      <c r="H99" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>318</v>
+      </c>
+      <c r="C100" t="s">
+        <v>319</v>
+      </c>
+      <c r="D100" t="s">
+        <v>320</v>
+      </c>
+      <c r="E100" t="s">
+        <v>315</v>
+      </c>
+      <c r="F100" t="s">
+        <v>316</v>
+      </c>
+      <c r="G100" t="s">
+        <v>321</v>
+      </c>
+      <c r="H100" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>322</v>
+      </c>
+      <c r="C101" t="s">
+        <v>323</v>
+      </c>
+      <c r="D101" t="s">
+        <v>324</v>
+      </c>
+      <c r="E101" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" t="s">
+        <v>316</v>
+      </c>
+      <c r="G101" t="s">
+        <v>325</v>
+      </c>
+      <c r="H101" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>326</v>
+      </c>
+      <c r="C102" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102" t="s">
+        <v>328</v>
+      </c>
+      <c r="E102" t="s">
+        <v>329</v>
+      </c>
+      <c r="F102" t="s">
+        <v>330</v>
+      </c>
+      <c r="G102" t="s">
+        <v>331</v>
+      </c>
+      <c r="H102" t="s">
+        <v>332</v>
+      </c>
+      <c r="I102" t="s">
+        <v>333</v>
+      </c>
+      <c r="J102" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>334</v>
+      </c>
+      <c r="C103" t="s">
+        <v>335</v>
+      </c>
+      <c r="D103" t="s">
+        <v>336</v>
+      </c>
+      <c r="E103" t="s">
+        <v>329</v>
+      </c>
+      <c r="F103" t="s">
+        <v>330</v>
+      </c>
+      <c r="G103" t="s">
+        <v>337</v>
+      </c>
+      <c r="H103" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>338</v>
+      </c>
+      <c r="C104" t="s">
+        <v>339</v>
+      </c>
+      <c r="D104" t="s">
+        <v>340</v>
+      </c>
+      <c r="E104" t="s">
+        <v>341</v>
+      </c>
+      <c r="F104" t="s">
+        <v>342</v>
+      </c>
+      <c r="G104" t="s">
+        <v>343</v>
+      </c>
+      <c r="H104" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>338</v>
+      </c>
+      <c r="C105" t="s">
+        <v>339</v>
+      </c>
+      <c r="D105" t="s">
+        <v>340</v>
+      </c>
+      <c r="E105" t="s">
+        <v>341</v>
+      </c>
+      <c r="F105" t="s">
+        <v>342</v>
+      </c>
+      <c r="G105" t="s">
+        <v>344</v>
+      </c>
+      <c r="H105" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>286</v>
+      </c>
+      <c r="C106" t="s">
+        <v>287</v>
+      </c>
+      <c r="D106" t="s">
+        <v>288</v>
+      </c>
+      <c r="E106" t="s">
+        <v>345</v>
+      </c>
+      <c r="F106" t="s">
+        <v>346</v>
+      </c>
+      <c r="G106" t="s">
+        <v>347</v>
+      </c>
+      <c r="H106" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" t="s">
+        <v>37</v>
+      </c>
+      <c r="D107" t="s">
+        <v>38</v>
+      </c>
+      <c r="E107" t="s">
+        <v>345</v>
+      </c>
+      <c r="F107" t="s">
+        <v>346</v>
+      </c>
+      <c r="G107" t="s">
+        <v>348</v>
+      </c>
+      <c r="H107" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>338</v>
+      </c>
+      <c r="C108" t="s">
+        <v>339</v>
+      </c>
+      <c r="D108" t="s">
+        <v>340</v>
+      </c>
+      <c r="E108" t="s">
+        <v>341</v>
+      </c>
+      <c r="F108" t="s">
+        <v>342</v>
+      </c>
+      <c r="G108" t="s">
+        <v>349</v>
+      </c>
+      <c r="H108" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>163</v>
+      </c>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109" t="s">
+        <v>350</v>
+      </c>
+      <c r="F109" t="s">
+        <v>351</v>
+      </c>
+      <c r="G109" t="s">
+        <v>352</v>
+      </c>
+      <c r="H109" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>59</v>
+      </c>
+      <c r="C110" t="s">
+        <v>60</v>
+      </c>
+      <c r="D110" t="s">
+        <v>61</v>
+      </c>
+      <c r="E110" t="s">
+        <v>353</v>
+      </c>
+      <c r="F110" t="s">
+        <v>354</v>
+      </c>
+      <c r="G110" t="s">
+        <v>355</v>
+      </c>
+      <c r="H110" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>89</v>
+      </c>
+      <c r="C111" t="s">
+        <v>90</v>
+      </c>
+      <c r="D111" t="s">
+        <v>91</v>
+      </c>
+      <c r="E111" t="s">
+        <v>350</v>
+      </c>
+      <c r="F111" t="s">
+        <v>351</v>
+      </c>
+      <c r="G111" t="s">
+        <v>356</v>
+      </c>
+      <c r="H111" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" t="s">
+        <v>17</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>215</v>
+      </c>
+      <c r="C112" t="s">
+        <v>216</v>
+      </c>
+      <c r="D112" t="s">
+        <v>217</v>
+      </c>
+      <c r="E112" t="s">
+        <v>350</v>
+      </c>
+      <c r="F112" t="s">
+        <v>351</v>
+      </c>
+      <c r="G112" t="s">
+        <v>357</v>
+      </c>
+      <c r="H112" t="s">
+        <v>16</v>
+      </c>
+      <c r="I112" t="s">
+        <v>17</v>
+      </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>358</v>
+      </c>
+      <c r="C113" t="s">
+        <v>359</v>
+      </c>
+      <c r="D113" t="s">
+        <v>360</v>
+      </c>
+      <c r="E113" t="s">
+        <v>350</v>
+      </c>
+      <c r="F113" t="s">
+        <v>351</v>
+      </c>
+      <c r="G113" t="s">
+        <v>361</v>
+      </c>
+      <c r="H113" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>362</v>
+      </c>
+      <c r="C114" t="s">
+        <v>363</v>
+      </c>
+      <c r="D114" t="s">
+        <v>364</v>
+      </c>
+      <c r="E114" t="s">
+        <v>365</v>
+      </c>
+      <c r="F114" t="s">
+        <v>366</v>
+      </c>
+      <c r="G114" t="s">
+        <v>367</v>
+      </c>
+      <c r="H114" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>163</v>
+      </c>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115" t="s">
+        <v>365</v>
+      </c>
+      <c r="F115" t="s">
+        <v>366</v>
+      </c>
+      <c r="G115" t="s">
+        <v>368</v>
+      </c>
+      <c r="H115" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" t="s">
+        <v>17</v>
+      </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>369</v>
+      </c>
+      <c r="C116" t="s">
+        <v>370</v>
+      </c>
+      <c r="D116" t="s">
+        <v>371</v>
+      </c>
+      <c r="E116" t="s">
+        <v>372</v>
+      </c>
+      <c r="F116" t="s">
+        <v>373</v>
+      </c>
+      <c r="G116" t="s">
+        <v>374</v>
+      </c>
+      <c r="H116" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>46</v>
+      </c>
+      <c r="C117" t="s">
+        <v>47</v>
+      </c>
+      <c r="D117" t="s">
+        <v>48</v>
+      </c>
+      <c r="E117" t="s">
+        <v>375</v>
+      </c>
+      <c r="F117" t="s">
+        <v>376</v>
+      </c>
+      <c r="G117" t="s">
+        <v>377</v>
+      </c>
+      <c r="H117" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>378</v>
+      </c>
+      <c r="C118" t="s">
+        <v>379</v>
+      </c>
+      <c r="D118" t="s">
+        <v>380</v>
+      </c>
+      <c r="E118" t="s">
+        <v>381</v>
+      </c>
+      <c r="F118" t="s">
+        <v>382</v>
+      </c>
+      <c r="G118" t="s">
+        <v>383</v>
+      </c>
+      <c r="H118" t="s">
+        <v>16</v>
+      </c>
+      <c r="I118" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119"/>
+      <c r="D119" t="s">
+        <v>385</v>
+      </c>
+      <c r="E119" t="s">
+        <v>365</v>
+      </c>
+      <c r="F119" t="s">
+        <v>366</v>
+      </c>
+      <c r="G119" t="s">
+        <v>386</v>
+      </c>
+      <c r="H119" t="s">
+        <v>16</v>
+      </c>
+      <c r="I119" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>148</v>
+      </c>
+      <c r="C120" t="s">
+        <v>149</v>
+      </c>
+      <c r="D120"/>
+      <c r="E120" t="s">
+        <v>375</v>
+      </c>
+      <c r="F120" t="s">
+        <v>376</v>
+      </c>
+      <c r="G120" t="s">
+        <v>387</v>
+      </c>
+      <c r="H120" t="s">
+        <v>151</v>
+      </c>
+      <c r="I120" t="s">
+        <v>152</v>
+      </c>
+      <c r="J120" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>388</v>
+      </c>
+      <c r="C121" t="s">
+        <v>389</v>
+      </c>
+      <c r="D121" t="s">
+        <v>390</v>
+      </c>
+      <c r="E121" t="s">
+        <v>140</v>
+      </c>
+      <c r="F121" t="s">
+        <v>141</v>
+      </c>
+      <c r="G121" t="s">
+        <v>391</v>
+      </c>
+      <c r="H121" t="s">
+        <v>16</v>
+      </c>
+      <c r="I121" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>46</v>
+      </c>
+      <c r="C122" t="s">
+        <v>47</v>
+      </c>
+      <c r="D122" t="s">
+        <v>48</v>
+      </c>
+      <c r="E122" t="s">
+        <v>381</v>
+      </c>
+      <c r="F122" t="s">
+        <v>382</v>
+      </c>
+      <c r="G122" t="s">
+        <v>392</v>
+      </c>
+      <c r="H122" t="s">
+        <v>16</v>
+      </c>
+      <c r="I122" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>89</v>
+      </c>
+      <c r="C123" t="s">
+        <v>90</v>
+      </c>
+      <c r="D123" t="s">
+        <v>91</v>
+      </c>
+      <c r="E123" t="s">
+        <v>259</v>
+      </c>
+      <c r="F123" t="s">
+        <v>260</v>
+      </c>
+      <c r="G123" t="s">
+        <v>393</v>
+      </c>
+      <c r="H123" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>305</v>
+      </c>
+      <c r="C124" t="s">
+        <v>306</v>
+      </c>
+      <c r="D124" t="s">
+        <v>307</v>
+      </c>
+      <c r="E124" t="s">
+        <v>394</v>
+      </c>
+      <c r="F124" t="s">
+        <v>395</v>
+      </c>
+      <c r="G124" t="s">
+        <v>396</v>
+      </c>
+      <c r="H124" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>197</v>
+      </c>
+      <c r="C125" t="s">
+        <v>198</v>
+      </c>
+      <c r="D125" t="s">
+        <v>199</v>
+      </c>
+      <c r="E125" t="s">
+        <v>365</v>
+      </c>
+      <c r="F125" t="s">
+        <v>366</v>
+      </c>
+      <c r="G125" t="s">
+        <v>397</v>
+      </c>
+      <c r="H125" t="s">
+        <v>16</v>
+      </c>
+      <c r="I125" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>46</v>
+      </c>
+      <c r="C126" t="s">
+        <v>47</v>
+      </c>
+      <c r="D126" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" t="s">
+        <v>398</v>
+      </c>
+      <c r="F126" t="s">
+        <v>399</v>
+      </c>
+      <c r="G126" t="s">
+        <v>400</v>
+      </c>
+      <c r="H126" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>318</v>
+      </c>
+      <c r="C127" t="s">
+        <v>319</v>
+      </c>
+      <c r="D127" t="s">
+        <v>320</v>
+      </c>
+      <c r="E127" t="s">
+        <v>375</v>
+      </c>
+      <c r="F127" t="s">
+        <v>376</v>
+      </c>
+      <c r="G127" t="s">
+        <v>401</v>
+      </c>
+      <c r="H127" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>402</v>
+      </c>
+      <c r="C128" t="s">
+        <v>403</v>
+      </c>
+      <c r="D128" t="s">
+        <v>404</v>
+      </c>
+      <c r="E128" t="s">
+        <v>375</v>
+      </c>
+      <c r="F128" t="s">
+        <v>376</v>
+      </c>
+      <c r="G128" t="s">
+        <v>405</v>
+      </c>
+      <c r="H128" t="s">
+        <v>16</v>
+      </c>
+      <c r="I128" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>46</v>
+      </c>
+      <c r="C129" t="s">
+        <v>47</v>
+      </c>
+      <c r="D129" t="s">
+        <v>48</v>
+      </c>
+      <c r="E129" t="s">
+        <v>375</v>
+      </c>
+      <c r="F129" t="s">
+        <v>376</v>
+      </c>
+      <c r="G129" t="s">
+        <v>406</v>
+      </c>
+      <c r="H129" t="s">
+        <v>16</v>
+      </c>
+      <c r="I129" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>59</v>
+      </c>
+      <c r="C130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D130" t="s">
+        <v>61</v>
+      </c>
+      <c r="E130" t="s">
+        <v>375</v>
+      </c>
+      <c r="F130" t="s">
+        <v>376</v>
+      </c>
+      <c r="G130" t="s">
+        <v>407</v>
+      </c>
+      <c r="H130" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>408</v>
+      </c>
+      <c r="C131" t="s">
+        <v>409</v>
+      </c>
+      <c r="D131" t="s">
+        <v>410</v>
+      </c>
+      <c r="E131" t="s">
+        <v>411</v>
+      </c>
+      <c r="F131" t="s">
+        <v>412</v>
+      </c>
+      <c r="G131" t="s">
+        <v>413</v>
+      </c>
+      <c r="H131" t="s">
+        <v>16</v>
+      </c>
+      <c r="I131" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>65</v>
+      </c>
+      <c r="C132" t="s">
+        <v>66</v>
+      </c>
+      <c r="D132"/>
+      <c r="E132" t="s">
+        <v>372</v>
+      </c>
+      <c r="F132" t="s">
+        <v>373</v>
+      </c>
+      <c r="G132" t="s">
+        <v>414</v>
+      </c>
+      <c r="H132" t="s">
+        <v>16</v>
+      </c>
+      <c r="I132" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>415</v>
+      </c>
+      <c r="C133"/>
+      <c r="D133" t="s">
+        <v>416</v>
+      </c>
+      <c r="E133" t="s">
+        <v>315</v>
+      </c>
+      <c r="F133" t="s">
+        <v>316</v>
+      </c>
+      <c r="G133" t="s">
+        <v>417</v>
+      </c>
+      <c r="H133" t="s">
+        <v>237</v>
+      </c>
+      <c r="I133" t="s">
+        <v>238</v>
+      </c>
+      <c r="J133" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>227</v>
+      </c>
+      <c r="C134" t="s">
+        <v>228</v>
+      </c>
+      <c r="D134" t="s">
+        <v>229</v>
+      </c>
+      <c r="E134" t="s">
+        <v>372</v>
+      </c>
+      <c r="F134" t="s">
+        <v>373</v>
+      </c>
+      <c r="G134" t="s">
+        <v>418</v>
+      </c>
+      <c r="H134" t="s">
+        <v>16</v>
+      </c>
+      <c r="I134" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>89</v>
+      </c>
+      <c r="C135" t="s">
+        <v>90</v>
+      </c>
+      <c r="D135" t="s">
+        <v>91</v>
+      </c>
+      <c r="E135" t="s">
+        <v>372</v>
+      </c>
+      <c r="F135" t="s">
+        <v>373</v>
+      </c>
+      <c r="G135" t="s">
+        <v>419</v>
+      </c>
+      <c r="H135" t="s">
+        <v>16</v>
+      </c>
+      <c r="I135" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>420</v>
+      </c>
+      <c r="C136" t="s">
+        <v>421</v>
+      </c>
+      <c r="D136" t="s">
+        <v>422</v>
+      </c>
+      <c r="E136" t="s">
+        <v>375</v>
+      </c>
+      <c r="F136" t="s">
+        <v>376</v>
+      </c>
+      <c r="G136" t="s">
+        <v>423</v>
+      </c>
+      <c r="H136" t="s">
+        <v>424</v>
+      </c>
+      <c r="I136" t="s">
+        <v>425</v>
+      </c>
+      <c r="J136" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>426</v>
+      </c>
+      <c r="C137" t="s">
+        <v>427</v>
+      </c>
+      <c r="D137" t="s">
+        <v>428</v>
+      </c>
+      <c r="E137" t="s">
+        <v>365</v>
+      </c>
+      <c r="F137" t="s">
+        <v>366</v>
+      </c>
+      <c r="G137" t="s">
+        <v>429</v>
+      </c>
+      <c r="H137" t="s">
+        <v>16</v>
+      </c>
+      <c r="I137" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>89</v>
+      </c>
+      <c r="C138" t="s">
+        <v>90</v>
+      </c>
+      <c r="D138" t="s">
+        <v>91</v>
+      </c>
+      <c r="E138" t="s">
+        <v>353</v>
+      </c>
+      <c r="F138" t="s">
+        <v>354</v>
+      </c>
+      <c r="G138" t="s">
+        <v>430</v>
+      </c>
+      <c r="H138" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>431</v>
+      </c>
+      <c r="C139" t="s">
+        <v>432</v>
+      </c>
+      <c r="D139" t="s">
+        <v>433</v>
+      </c>
+      <c r="E139" t="s">
+        <v>394</v>
+      </c>
+      <c r="F139" t="s">
+        <v>395</v>
+      </c>
+      <c r="G139" t="s">
+        <v>434</v>
+      </c>
+      <c r="H139" t="s">
+        <v>16</v>
+      </c>
+      <c r="I139" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>293</v>
+      </c>
+      <c r="C140" t="s">
+        <v>294</v>
+      </c>
+      <c r="D140" t="s">
+        <v>295</v>
+      </c>
+      <c r="E140" t="s">
+        <v>375</v>
+      </c>
+      <c r="F140" t="s">
+        <v>376</v>
+      </c>
+      <c r="G140" t="s">
+        <v>435</v>
+      </c>
+      <c r="H140" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>436</v>
+      </c>
+      <c r="C141"/>
+      <c r="D141" t="s">
+        <v>437</v>
+      </c>
+      <c r="E141" t="s">
+        <v>398</v>
+      </c>
+      <c r="F141" t="s">
+        <v>399</v>
+      </c>
+      <c r="G141" t="s">
+        <v>438</v>
+      </c>
+      <c r="H141" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>46</v>
+      </c>
+      <c r="C142" t="s">
+        <v>47</v>
+      </c>
+      <c r="D142" t="s">
+        <v>48</v>
+      </c>
+      <c r="E142" t="s">
+        <v>375</v>
+      </c>
+      <c r="F142" t="s">
+        <v>376</v>
+      </c>
+      <c r="G142" t="s">
+        <v>439</v>
+      </c>
+      <c r="H142" t="s">
+        <v>16</v>
+      </c>
+      <c r="I142" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>293</v>
+      </c>
+      <c r="C143" t="s">
+        <v>294</v>
+      </c>
+      <c r="D143" t="s">
+        <v>295</v>
+      </c>
+      <c r="E143" t="s">
+        <v>375</v>
+      </c>
+      <c r="F143" t="s">
+        <v>376</v>
+      </c>
+      <c r="G143" t="s">
+        <v>440</v>
+      </c>
+      <c r="H143" t="s">
+        <v>16</v>
+      </c>
+      <c r="I143" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>431</v>
+      </c>
+      <c r="C144" t="s">
+        <v>432</v>
+      </c>
+      <c r="D144" t="s">
+        <v>433</v>
+      </c>
+      <c r="E144" t="s">
+        <v>394</v>
+      </c>
+      <c r="F144" t="s">
+        <v>395</v>
+      </c>
+      <c r="G144" t="s">
+        <v>441</v>
+      </c>
+      <c r="H144" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>181</v>
+      </c>
+      <c r="C145" t="s">
+        <v>182</v>
+      </c>
+      <c r="D145" t="s">
+        <v>183</v>
+      </c>
+      <c r="E145" t="s">
+        <v>365</v>
+      </c>
+      <c r="F145" t="s">
+        <v>366</v>
+      </c>
+      <c r="G145" t="s">
+        <v>442</v>
+      </c>
+      <c r="H145" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>227</v>
+      </c>
+      <c r="C146" t="s">
+        <v>228</v>
+      </c>
+      <c r="D146" t="s">
+        <v>229</v>
+      </c>
+      <c r="E146" t="s">
+        <v>372</v>
+      </c>
+      <c r="F146" t="s">
+        <v>373</v>
+      </c>
+      <c r="G146" t="s">
+        <v>443</v>
+      </c>
+      <c r="H146" t="s">
+        <v>16</v>
+      </c>
+      <c r="I146" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>426</v>
+      </c>
+      <c r="C147" t="s">
+        <v>427</v>
+      </c>
+      <c r="D147" t="s">
+        <v>428</v>
+      </c>
+      <c r="E147" t="s">
+        <v>365</v>
+      </c>
+      <c r="F147" t="s">
+        <v>366</v>
+      </c>
+      <c r="G147" t="s">
+        <v>444</v>
+      </c>
+      <c r="H147" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147" t="s">
+        <v>17</v>
+      </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>445</v>
+      </c>
+      <c r="C148" t="s">
+        <v>446</v>
+      </c>
+      <c r="D148" t="s">
+        <v>447</v>
+      </c>
+      <c r="E148" t="s">
+        <v>398</v>
+      </c>
+      <c r="F148" t="s">
+        <v>399</v>
+      </c>
+      <c r="G148" t="s">
+        <v>448</v>
+      </c>
+      <c r="H148" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" t="s">
+        <v>17</v>
+      </c>
+      <c r="J148" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>46</v>
+      </c>
+      <c r="C149" t="s">
+        <v>47</v>
+      </c>
+      <c r="D149" t="s">
+        <v>48</v>
+      </c>
+      <c r="E149" t="s">
+        <v>375</v>
+      </c>
+      <c r="F149" t="s">
+        <v>376</v>
+      </c>
+      <c r="G149" t="s">
+        <v>449</v>
+      </c>
+      <c r="H149" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149" t="s">
+        <v>17</v>
+      </c>
+      <c r="J149" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>450</v>
+      </c>
+      <c r="C150" t="s">
+        <v>451</v>
+      </c>
+      <c r="D150" t="s">
+        <v>452</v>
+      </c>
+      <c r="E150" t="s">
+        <v>365</v>
+      </c>
+      <c r="F150" t="s">
+        <v>366</v>
+      </c>
+      <c r="G150" t="s">
+        <v>453</v>
+      </c>
+      <c r="H150" t="s">
+        <v>16</v>
+      </c>
+      <c r="I150" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>240</v>
+      </c>
+      <c r="C151"/>
+      <c r="D151" t="s">
+        <v>241</v>
+      </c>
+      <c r="E151" t="s">
+        <v>394</v>
+      </c>
+      <c r="F151" t="s">
+        <v>395</v>
+      </c>
+      <c r="G151" t="s">
+        <v>454</v>
+      </c>
+      <c r="H151" t="s">
+        <v>16</v>
+      </c>
+      <c r="I151" t="s">
+        <v>17</v>
+      </c>
+      <c r="J151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>455</v>
+      </c>
+      <c r="C152" t="s">
+        <v>456</v>
+      </c>
+      <c r="D152" t="s">
+        <v>457</v>
+      </c>
+      <c r="E152" t="s">
+        <v>411</v>
+      </c>
+      <c r="F152" t="s">
+        <v>412</v>
+      </c>
+      <c r="G152" t="s">
+        <v>458</v>
+      </c>
+      <c r="H152" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
